--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99446DA9-8640-48C1-A2F6-0A73D95A3064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282FC6D8-41A7-4C5A-9A28-C41F8D9D3E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-16200" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="28530" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="463">
   <si>
     <t>2024/25</t>
   </si>
@@ -1423,6 +1423,9 @@
   </si>
   <si>
     <t>22/08 - 28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08 - 04/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L445"/>
+  <dimension ref="A1:L446"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10964,14 +10967,34 @@
       <c r="C445" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D445" s="1">
+      <c r="D445" s="8">
         <v>2216</v>
       </c>
-      <c r="E445" s="1">
-        <v>0</v>
-      </c>
-      <c r="F445" s="1">
-        <v>2216</v>
+      <c r="E445" s="8">
+        <v>19</v>
+      </c>
+      <c r="F445" s="8">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A446" s="35">
+        <v>27</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C446" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="D446" s="8">
+        <v>1664</v>
+      </c>
+      <c r="E446" s="8">
+        <v>0</v>
+      </c>
+      <c r="F446" s="8">
+        <v>1664</v>
       </c>
     </row>
   </sheetData>
@@ -10982,7 +11005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L445"/>
+  <dimension ref="A1:L446"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19791,10 +19814,10 @@
         <v>19714</v>
       </c>
       <c r="E437" s="8">
-        <v>-512</v>
+        <v>-200</v>
       </c>
       <c r="F437" s="8">
-        <v>19202</v>
+        <v>19514</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -19811,10 +19834,10 @@
         <v>15115</v>
       </c>
       <c r="E438" s="8">
-        <v>6013</v>
+        <v>5368</v>
       </c>
       <c r="F438" s="8">
-        <v>21128</v>
+        <v>20483</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -19831,10 +19854,10 @@
         <v>14395</v>
       </c>
       <c r="E439" s="8">
-        <v>-462</v>
+        <v>-338</v>
       </c>
       <c r="F439" s="8">
-        <v>13933</v>
+        <v>14057</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -19851,10 +19874,10 @@
         <v>9792</v>
       </c>
       <c r="E440" s="8">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="F440" s="8">
-        <v>9943</v>
+        <v>9871</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -19871,10 +19894,10 @@
         <v>5680</v>
       </c>
       <c r="E441" s="8">
-        <v>5198</v>
+        <v>5197</v>
       </c>
       <c r="F441" s="8">
-        <v>10878</v>
+        <v>10877</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -19947,14 +19970,34 @@
       <c r="C445" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D445" s="1">
+      <c r="D445" s="8">
         <v>5698</v>
       </c>
-      <c r="E445" s="1">
-        <v>0</v>
-      </c>
-      <c r="F445" s="1">
+      <c r="E445" s="8">
+        <v>0</v>
+      </c>
+      <c r="F445" s="8">
         <v>5698</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A446" s="3">
+        <v>27</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C446" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="D446" s="8">
+        <v>5028</v>
+      </c>
+      <c r="E446" s="8">
+        <v>0</v>
+      </c>
+      <c r="F446" s="8">
+        <v>5028</v>
       </c>
     </row>
   </sheetData>

--- a/Codex Oilseeds.xlsx
+++ b/Codex Oilseeds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\grain-data-intelligence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282FC6D8-41A7-4C5A-9A28-C41F8D9D3E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65945F8A-6BFF-4A32-83E0-EB87DB2EA3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28530" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3291B9F-AFF8-4BC9-9580-4EC86BA51820}"/>
   </bookViews>
   <sheets>
     <sheet name="Sunflowers" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="468">
   <si>
     <t>2024/25</t>
   </si>
@@ -1426,6 +1426,21 @@
   </si>
   <si>
     <t>29/08 - 04/09/2026</t>
+  </si>
+  <si>
+    <t>05/09 - 11/09/2026</t>
+  </si>
+  <si>
+    <t>12/09 - 18/09/2026</t>
+  </si>
+  <si>
+    <t>19/09 - 25/09/2026</t>
+  </si>
+  <si>
+    <t>26/09 - 02/10/2026</t>
+  </si>
+  <si>
+    <t>03/10 - 09/10/2026</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1679,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1718,6 +1733,10 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2001,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22352F53-108E-46E1-867D-0BA510AFEED4}">
-  <dimension ref="A1:L446"/>
+  <dimension ref="A1:L451"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10464,16 +10483,16 @@
       <c r="B420" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C420" s="5" t="s">
+      <c r="C420" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="D420" s="6">
+      <c r="D420" s="38">
         <v>8059</v>
       </c>
-      <c r="E420" s="6">
+      <c r="E420" s="38">
         <v>742</v>
       </c>
-      <c r="F420" s="6">
+      <c r="F420" s="38">
         <v>8801</v>
       </c>
     </row>
@@ -10484,16 +10503,16 @@
       <c r="B421" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C421" s="7" t="s">
+      <c r="C421" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D421" s="8">
+      <c r="D421" s="39">
         <v>22734</v>
       </c>
-      <c r="E421" s="8">
+      <c r="E421" s="39">
         <v>922</v>
       </c>
-      <c r="F421" s="8">
+      <c r="F421" s="39">
         <v>23656</v>
       </c>
     </row>
@@ -10504,16 +10523,16 @@
       <c r="B422" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C422" s="7" t="s">
+      <c r="C422" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="D422" s="8">
+      <c r="D422" s="39">
         <v>26484</v>
       </c>
-      <c r="E422" s="8">
+      <c r="E422" s="39">
         <v>3923</v>
       </c>
-      <c r="F422" s="8">
+      <c r="F422" s="39">
         <v>30407</v>
       </c>
     </row>
@@ -10524,16 +10543,16 @@
       <c r="B423" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C423" s="7" t="s">
+      <c r="C423" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D423" s="8">
+      <c r="D423" s="39">
         <v>17047</v>
       </c>
-      <c r="E423" s="8">
+      <c r="E423" s="39">
         <v>2351</v>
       </c>
-      <c r="F423" s="8">
+      <c r="F423" s="39">
         <v>19398</v>
       </c>
     </row>
@@ -10544,16 +10563,16 @@
       <c r="B424" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C424" s="7" t="s">
+      <c r="C424" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D424" s="8">
+      <c r="D424" s="39">
         <v>39182</v>
       </c>
-      <c r="E424" s="8">
+      <c r="E424" s="39">
         <v>2818</v>
       </c>
-      <c r="F424" s="8">
+      <c r="F424" s="39">
         <v>42000</v>
       </c>
     </row>
@@ -10564,16 +10583,16 @@
       <c r="B425" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C425" s="7" t="s">
+      <c r="C425" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D425" s="8">
+      <c r="D425" s="39">
         <v>75766</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425" s="39">
         <v>3686</v>
       </c>
-      <c r="F425" s="8">
+      <c r="F425" s="39">
         <v>79452</v>
       </c>
     </row>
@@ -10584,16 +10603,16 @@
       <c r="B426" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C426" s="7" t="s">
+      <c r="C426" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="D426" s="8">
+      <c r="D426" s="39">
         <v>56615</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426" s="39">
         <v>651</v>
       </c>
-      <c r="F426" s="8">
+      <c r="F426" s="39">
         <v>57266</v>
       </c>
     </row>
@@ -10604,16 +10623,16 @@
       <c r="B427" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C427" s="7" t="s">
+      <c r="C427" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D427" s="8">
+      <c r="D427" s="39">
         <v>33342</v>
       </c>
-      <c r="E427" s="8">
+      <c r="E427" s="39">
         <v>2446</v>
       </c>
-      <c r="F427" s="8">
+      <c r="F427" s="39">
         <v>35788</v>
       </c>
     </row>
@@ -10624,16 +10643,16 @@
       <c r="B428" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C428" s="7" t="s">
+      <c r="C428" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="D428" s="8">
+      <c r="D428" s="39">
         <v>55113</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428" s="39">
         <v>1637</v>
       </c>
-      <c r="F428" s="8">
+      <c r="F428" s="39">
         <v>56750</v>
       </c>
     </row>
@@ -10644,16 +10663,16 @@
       <c r="B429" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C429" s="7" t="s">
+      <c r="C429" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D429" s="8">
+      <c r="D429" s="39">
         <v>44476</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429" s="39">
         <v>-252</v>
       </c>
-      <c r="F429" s="8">
+      <c r="F429" s="39">
         <v>44224</v>
       </c>
     </row>
@@ -10664,16 +10683,16 @@
       <c r="B430" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="D430" s="8">
+      <c r="D430" s="39">
         <v>99689</v>
       </c>
-      <c r="E430" s="8">
+      <c r="E430" s="39">
         <v>1383</v>
       </c>
-      <c r="F430" s="8">
+      <c r="F430" s="39">
         <v>101072</v>
       </c>
     </row>
@@ -10684,16 +10703,16 @@
       <c r="B431" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C431" s="7" t="s">
+      <c r="C431" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D431" s="8">
+      <c r="D431" s="39">
         <v>83530</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431" s="39">
         <v>2259</v>
       </c>
-      <c r="F431" s="8">
+      <c r="F431" s="39">
         <v>85789</v>
       </c>
     </row>
@@ -10704,16 +10723,16 @@
       <c r="B432" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C432" s="7" t="s">
+      <c r="C432" s="34" t="s">
         <v>448</v>
       </c>
-      <c r="D432" s="8">
+      <c r="D432" s="39">
         <v>59752</v>
       </c>
-      <c r="E432" s="8">
+      <c r="E432" s="39">
         <v>711</v>
       </c>
-      <c r="F432" s="8">
+      <c r="F432" s="39">
         <v>60463</v>
       </c>
     </row>
@@ -10724,16 +10743,16 @@
       <c r="B433" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C433" s="7" t="s">
+      <c r="C433" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="D433" s="8">
+      <c r="D433" s="39">
         <v>40427</v>
       </c>
-      <c r="E433" s="8">
+      <c r="E433" s="39">
         <v>304</v>
       </c>
-      <c r="F433" s="8">
+      <c r="F433" s="39">
         <v>40731</v>
       </c>
     </row>
@@ -10744,16 +10763,16 @@
       <c r="B434" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C434" s="7" t="s">
+      <c r="C434" s="34" t="s">
         <v>450</v>
       </c>
-      <c r="D434" s="8">
+      <c r="D434" s="39">
         <v>36123</v>
       </c>
-      <c r="E434" s="8">
+      <c r="E434" s="39">
         <v>315</v>
       </c>
-      <c r="F434" s="8">
+      <c r="F434" s="39">
         <v>36438</v>
       </c>
     </row>
@@ -10764,16 +10783,16 @@
       <c r="B435" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C435" s="7" t="s">
+      <c r="C435" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="D435" s="8">
+      <c r="D435" s="39">
         <v>28792</v>
       </c>
-      <c r="E435" s="8">
+      <c r="E435" s="39">
         <v>-343</v>
       </c>
-      <c r="F435" s="8">
+      <c r="F435" s="39">
         <v>28449</v>
       </c>
     </row>
@@ -10784,16 +10803,16 @@
       <c r="B436" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C436" s="7" t="s">
+      <c r="C436" s="34" t="s">
         <v>452</v>
       </c>
-      <c r="D436" s="8">
+      <c r="D436" s="39">
         <v>10316</v>
       </c>
-      <c r="E436" s="8">
+      <c r="E436" s="39">
         <v>1451</v>
       </c>
-      <c r="F436" s="8">
+      <c r="F436" s="39">
         <v>11767</v>
       </c>
     </row>
@@ -10804,17 +10823,17 @@
       <c r="B437" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C437" s="7" t="s">
+      <c r="C437" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="D437" s="8">
+      <c r="D437" s="39">
         <v>12812</v>
       </c>
-      <c r="E437" s="8">
-        <v>-20</v>
-      </c>
-      <c r="F437" s="8">
-        <v>12792</v>
+      <c r="E437" s="39">
+        <v>-57</v>
+      </c>
+      <c r="F437" s="39">
+        <v>12755</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -10824,16 +10843,16 @@
       <c r="B438" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C438" s="7" t="s">
+      <c r="C438" s="34" t="s">
         <v>454</v>
       </c>
-      <c r="D438" s="8">
+      <c r="D438" s="39">
         <v>11333</v>
       </c>
-      <c r="E438" s="8">
+      <c r="E438" s="39">
         <v>363</v>
       </c>
-      <c r="F438" s="8">
+      <c r="F438" s="39">
         <v>11696</v>
       </c>
     </row>
@@ -10844,17 +10863,17 @@
       <c r="B439" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C439" s="7" t="s">
+      <c r="C439" s="34" t="s">
         <v>455</v>
       </c>
-      <c r="D439" s="8">
+      <c r="D439" s="39">
         <v>8619</v>
       </c>
-      <c r="E439" s="8">
-        <v>9</v>
-      </c>
-      <c r="F439" s="8">
-        <v>8628</v>
+      <c r="E439" s="39">
+        <v>-25</v>
+      </c>
+      <c r="F439" s="39">
+        <v>8594</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -10864,16 +10883,16 @@
       <c r="B440" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C440" s="7" t="s">
+      <c r="C440" s="34" t="s">
         <v>456</v>
       </c>
-      <c r="D440" s="8">
+      <c r="D440" s="39">
         <v>7083</v>
       </c>
-      <c r="E440" s="8">
+      <c r="E440" s="39">
         <v>391</v>
       </c>
-      <c r="F440" s="8">
+      <c r="F440" s="39">
         <v>7474</v>
       </c>
     </row>
@@ -10884,16 +10903,16 @@
       <c r="B441" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C441" s="7" t="s">
+      <c r="C441" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="D441" s="8">
+      <c r="D441" s="39">
         <v>5251</v>
       </c>
-      <c r="E441" s="8">
+      <c r="E441" s="39">
         <v>122</v>
       </c>
-      <c r="F441" s="8">
+      <c r="F441" s="39">
         <v>5373</v>
       </c>
     </row>
@@ -10904,17 +10923,17 @@
       <c r="B442" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C442" s="7" t="s">
+      <c r="C442" s="34" t="s">
         <v>458</v>
       </c>
-      <c r="D442" s="8">
+      <c r="D442" s="39">
         <v>4703</v>
       </c>
-      <c r="E442" s="8">
-        <v>389</v>
-      </c>
-      <c r="F442" s="8">
-        <v>5092</v>
+      <c r="E442" s="39">
+        <v>-103</v>
+      </c>
+      <c r="F442" s="39">
+        <v>4600</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -10924,17 +10943,17 @@
       <c r="B443" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C443" s="7" t="s">
+      <c r="C443" s="34" t="s">
         <v>459</v>
       </c>
-      <c r="D443" s="8">
+      <c r="D443" s="39">
         <v>2674</v>
       </c>
-      <c r="E443" s="8">
-        <v>0</v>
-      </c>
-      <c r="F443" s="8">
-        <v>2674</v>
+      <c r="E443" s="39">
+        <v>-450</v>
+      </c>
+      <c r="F443" s="39">
+        <v>2224</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -10944,17 +10963,17 @@
       <c r="B444" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C444" s="7" t="s">
+      <c r="C444" s="34" t="s">
         <v>460</v>
       </c>
-      <c r="D444" s="8">
+      <c r="D444" s="39">
         <v>2921</v>
       </c>
-      <c r="E444" s="8">
-        <v>0</v>
-      </c>
-      <c r="F444" s="8">
-        <v>2921</v>
+      <c r="E444" s="39">
+        <v>-136</v>
+      </c>
+      <c r="F444" s="39">
+        <v>2785</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -10964,17 +10983,17 @@
       <c r="B445" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C445" s="2" t="s">
+      <c r="C445" s="34" t="s">
         <v>461</v>
       </c>
-      <c r="D445" s="8">
+      <c r="D445" s="39">
         <v>2216</v>
       </c>
-      <c r="E445" s="8">
-        <v>19</v>
-      </c>
-      <c r="F445" s="8">
-        <v>2235</v>
+      <c r="E445" s="39">
+        <v>-14</v>
+      </c>
+      <c r="F445" s="39">
+        <v>2202</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -10984,17 +11003,117 @@
       <c r="B446" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C446" s="35" t="s">
+      <c r="C446" s="34" t="s">
         <v>462</v>
       </c>
-      <c r="D446" s="8">
+      <c r="D446" s="39">
         <v>1664</v>
       </c>
-      <c r="E446" s="8">
-        <v>0</v>
-      </c>
-      <c r="F446" s="8">
-        <v>1664</v>
+      <c r="E446" s="39">
+        <v>-33</v>
+      </c>
+      <c r="F446" s="39">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A447" s="35">
+        <v>28</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C447" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="D447" s="39">
+        <v>822</v>
+      </c>
+      <c r="E447" s="39">
+        <v>0</v>
+      </c>
+      <c r="F447" s="39">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A448" s="35">
+        <v>29</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C448" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="D448" s="39">
+        <v>543</v>
+      </c>
+      <c r="E448" s="39">
+        <v>0</v>
+      </c>
+      <c r="F448" s="39">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A449" s="35">
+        <v>30</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C449" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="D449" s="39">
+        <v>319</v>
+      </c>
+      <c r="E449" s="39">
+        <v>28</v>
+      </c>
+      <c r="F449" s="39">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A450" s="35">
+        <v>31</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C450" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="D450" s="39">
+        <v>708</v>
+      </c>
+      <c r="E450" s="39">
+        <v>0</v>
+      </c>
+      <c r="F450" s="39">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A451" s="35">
+        <v>32</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C451" s="35" t="s">
+        <v>467</v>
+      </c>
+      <c r="D451" s="40">
+        <v>874</v>
+      </c>
+      <c r="E451" s="40">
+        <v>0</v>
+      </c>
+      <c r="F451" s="40">
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -11005,7 +11124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76B85704-FA9F-47C9-8710-67621FBDF428}">
-  <dimension ref="A1:L446"/>
+  <dimension ref="A1:L451"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -19534,10 +19653,10 @@
         <v>14216</v>
       </c>
       <c r="E423" s="8">
-        <v>1821</v>
+        <v>2615</v>
       </c>
       <c r="F423" s="8">
-        <v>16037</v>
+        <v>16831</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -19614,10 +19733,10 @@
         <v>64774</v>
       </c>
       <c r="E427" s="8">
-        <v>11131</v>
+        <v>15118</v>
       </c>
       <c r="F427" s="8">
-        <v>75905</v>
+        <v>79892</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -19714,10 +19833,10 @@
         <v>370449</v>
       </c>
       <c r="E432" s="8">
-        <v>25426</v>
+        <v>29697</v>
       </c>
       <c r="F432" s="8">
-        <v>395875</v>
+        <v>400146</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -19794,10 +19913,10 @@
         <v>26534</v>
       </c>
       <c r="E436" s="8">
-        <v>6250</v>
+        <v>7513</v>
       </c>
       <c r="F436" s="8">
-        <v>32784</v>
+        <v>34047</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -19874,10 +19993,10 @@
         <v>9792</v>
       </c>
       <c r="E440" s="8">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="F440" s="8">
-        <v>9871</v>
+        <v>9941</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -19894,10 +20013,10 @@
         <v>5680</v>
       </c>
       <c r="E441" s="8">
-        <v>5197</v>
+        <v>4245</v>
       </c>
       <c r="F441" s="8">
-        <v>10877</v>
+        <v>9925</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -19914,10 +20033,10 @@
         <v>5926</v>
       </c>
       <c r="E442" s="8">
-        <v>107</v>
+        <v>341</v>
       </c>
       <c r="F442" s="8">
-        <v>6033</v>
+        <v>6267</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -19934,10 +20053,10 @@
         <v>4977</v>
       </c>
       <c r="E443" s="8">
-        <v>0</v>
+        <v>-444</v>
       </c>
       <c r="F443" s="8">
-        <v>4977</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -19954,10 +20073,10 @@
         <v>6836</v>
       </c>
       <c r="E444" s="8">
-        <v>0</v>
+        <v>-641</v>
       </c>
       <c r="F444" s="8">
-        <v>6836</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -19967,17 +20086,17 @@
       <c r="B445" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C445" s="2" t="s">
+      <c r="C445" s="7" t="s">
         <v>461</v>
       </c>
       <c r="D445" s="8">
         <v>5698</v>
       </c>
       <c r="E445" s="8">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F445" s="8">
-        <v>5698</v>
+        <v>5762</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -19987,17 +20106,117 @@
       <c r="B446" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C446" s="35" t="s">
+      <c r="C446" s="7" t="s">
         <v>462</v>
       </c>
       <c r="D446" s="8">
         <v>5028</v>
       </c>
       <c r="E446" s="8">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="F446" s="8">
-        <v>5028</v>
+        <v>5233</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A447" s="3">
+        <v>28</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C447" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D447" s="8">
+        <v>3337</v>
+      </c>
+      <c r="E447" s="8">
+        <v>0</v>
+      </c>
+      <c r="F447" s="8">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A448" s="3">
+        <v>29</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C448" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D448" s="8">
+        <v>3221</v>
+      </c>
+      <c r="E448" s="8">
+        <v>492</v>
+      </c>
+      <c r="F448" s="8">
+        <v>3713</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A449" s="3">
+        <v>30</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C449" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D449" s="8">
+        <v>6300</v>
+      </c>
+      <c r="E449" s="8">
+        <v>275</v>
+      </c>
+      <c r="F449" s="8">
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A450" s="3">
+        <v>31</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C450" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D450" s="8">
+        <v>2298</v>
+      </c>
+      <c r="E450" s="8">
+        <v>11</v>
+      </c>
+      <c r="F450" s="8">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A451" s="3">
+        <v>32</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D451" s="1">
+        <v>3824</v>
+      </c>
+      <c r="E451" s="1">
+        <v>0</v>
+      </c>
+      <c r="F451" s="1">
+        <v>3824</v>
       </c>
     </row>
   </sheetData>
@@ -20016,6 +20235,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010075ECE796D7EABA42BC0DB2CA73C7CE00" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e2ecee1b3d34a959aed38d5dc4c878f4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8" xmlns:ns3="ae149517-eeaa-465d-b3b6-396a1e23bc6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9af26d9f7c79c0f2a842447557dfee25" ns2:_="" ns3:_="">
     <xsd:import namespace="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
@@ -20242,17 +20472,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ae149517-eeaa-465d-b3b6-396a1e23bc6e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57FC624A-B42B-46E4-AEE9-C5C071C6FB17}">
   <ds:schemaRefs>
@@ -20262,6 +20481,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
+    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{409921FC-0447-4F0C-872E-CE24E2C3DE02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20278,15 +20508,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D929ACA6-317A-4DC6-98B5-19C43F6EFDF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fe4ae0e-3af2-48f1-b2fd-da4a302e5eb8"/>
-    <ds:schemaRef ds:uri="ae149517-eeaa-465d-b3b6-396a1e23bc6e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>